--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_378_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_378_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8085</v>
+        <v>2.4509</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7509</v>
+        <v>1.6958</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0576</v>
+        <v>0.7552</v>
       </c>
       <c r="G2" t="n">
         <v>2.8207</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3642</v>
+        <v>0.0066</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.094</v>
+        <v>-0.1491</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4582</v>
+        <v>0.1557</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>A. AVRAMOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9157</v>
+        <v>0.9859</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9033</v>
+        <v>1.7822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0124</v>
+        <v>-0.7962</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1895</v>
+        <v>0.6617</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4332</v>
+        <v>-0.9243</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6227</v>
+        <v>1.586</v>
       </c>
       <c r="J3" t="n">
-        <v>0.089</v>
+        <v>1.7624</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1231</v>
+        <v>-0.9845</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.0341</v>
+        <v>2.7469</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2785</v>
+        <v>-1.1007</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3101</v>
+        <v>0.0602</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5886</v>
+        <v>-1.1609</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.9432</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>1.69</v>
+        <v>-0.1397</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0227</v>
+        <v>0.0198</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6673</v>
+        <v>-0.1595</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4306</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3952</v>
+        <v>0.5802</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5062</v>
+        <v>1.4547</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.111</v>
+        <v>-0.8746</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7877</v>
+        <v>0.7935</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1056</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8932</v>
+        <v>0.1105</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1881</v>
+        <v>1.6547</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07770000000000001</v>
+        <v>1.1161</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1104</v>
+        <v>0.5386</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9758</v>
+        <v>-0.8612</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0279</v>
+        <v>-0.4331</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0037</v>
+        <v>-0.4281</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8066</v>
+        <v>0.163</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1221</v>
+        <v>-0.3418</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6844</v>
+        <v>0.5048</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3558</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3548</v>
+        <v>0.1743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7589</v>
+        <v>0.4197</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4041</v>
+        <v>-0.2454</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7935</v>
+        <v>-0.7877</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.1056</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1105</v>
+        <v>-0.8932</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6547</v>
+        <v>0.1881</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1161</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5386</v>
+        <v>0.1104</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8612</v>
+        <v>-0.9758</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4331</v>
+        <v>0.0279</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4281</v>
+        <v>-1.0037</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0624</v>
+        <v>0.5856</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0376</v>
+        <v>0.0356</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>1.3558</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. AVRAMOVIC</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2497</v>
+        <v>-0.3332</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2476</v>
+        <v>-0.2448</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9979</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6617</v>
+        <v>-0.1895</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9243</v>
+        <v>1.4332</v>
       </c>
       <c r="I6" t="n">
-        <v>1.586</v>
+        <v>-1.6227</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7624</v>
+        <v>0.089</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9845</v>
+        <v>1.1231</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7469</v>
+        <v>-1.0341</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1007</v>
+        <v>-0.2785</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0602</v>
+        <v>0.3101</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1609</v>
+        <v>-0.5886</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.876</v>
+        <v>0.4411</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5149</v>
+        <v>-0.1254</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3611</v>
+        <v>0.5665</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.4306</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.467</v>
+        <v>-0.3827</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1429</v>
+        <v>-1.025</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5193</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0523</v>
+        <v>0.1366</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4257</v>
+        <v>0.3921</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>K. KONDIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8411</v>
+        <v>-0.4203</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1987</v>
+        <v>-0.5693</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3576</v>
+        <v>0.149</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5937</v>
+        <v>-0.7742</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8079</v>
+        <v>0.0289</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2142</v>
+        <v>-0.8031</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7863</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0822</v>
+        <v>-0.0751</v>
       </c>
       <c r="N8" t="n">
         <v>-0.0216</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1038</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9124</v>
+        <v>0.3539</v>
       </c>
       <c r="T8" t="n">
-        <v>0.637</v>
+        <v>0.1298</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2754</v>
+        <v>0.224</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. KONDIC</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9833</v>
+        <v>-0.8922</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9979</v>
+        <v>-3.1287</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0145</v>
+        <v>2.2365</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7742</v>
+        <v>1.6092</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0289</v>
+        <v>-1.6098</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8031</v>
+        <v>3.219</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6991000000000001</v>
+        <v>1.0658</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0504</v>
+        <v>-1.9522</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7495000000000001</v>
+        <v>3.018</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0751</v>
+        <v>0.5434</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0216</v>
+        <v>0.3424</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0535</v>
+        <v>0.201</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2091</v>
+        <v>-0.3648</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0896</v>
+        <v>0.3504</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8158</v>
+        <v>-1.5481</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7498</v>
+        <v>-1.6705</v>
       </c>
       <c r="F10" t="n">
-        <v>1.934</v>
+        <v>0.1224</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6092</v>
+        <v>-0.5937</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6098</v>
+        <v>-0.8079</v>
       </c>
       <c r="I10" t="n">
-        <v>3.219</v>
+        <v>0.2142</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0658</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9522</v>
+        <v>-0.7863</v>
       </c>
       <c r="L10" t="n">
-        <v>3.018</v>
+        <v>0.1104</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5434</v>
+        <v>0.0822</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3424</v>
+        <v>-0.0216</v>
       </c>
       <c r="O10" t="n">
-        <v>0.201</v>
+        <v>0.1038</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7834</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2885</v>
+        <v>0.2054</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3364</v>
+        <v>0.1652</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0479</v>
+        <v>0.0402</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1329</v>
+        <v>-1.5796</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9719</v>
+        <v>-0.5867</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.161</v>
+        <v>-0.9929</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7118</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4933</v>
+        <v>0.06</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2908</v>
+        <v>0.0944</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.477</v>
+        <v>-1.9499</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9845</v>
+        <v>-2.5245</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5075</v>
+        <v>0.5747</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6583</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.427</v>
+        <v>0.1002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.507</v>
+        <v>-0.047</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08</v>
+        <v>0.1472</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3995</v>
+        <v>-2.611</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1051</v>
+        <v>-2.7198</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2944</v>
+        <v>0.1089</v>
       </c>
       <c r="G13" t="n">
         <v>1.0635</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8266</v>
+        <v>-1.0381</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4936</v>
+        <v>-1.1084</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.333</v>
+        <v>0.0703</v>
       </c>
       <c r="V13" t="n">
         <v>2.0026</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.3927</v>
+        <v>-5.525700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.9839</v>
+        <v>-7.1169</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5911</v>
+        <v>1.5915</v>
       </c>
       <c r="G14" t="n">
         <v>0.7140999999999993</v>
@@ -1522,10 +1522,10 @@
         <v>4.5919</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.282799999999999</v>
+        <v>-2.2828</v>
       </c>
       <c r="L14" t="n">
-        <v>6.874700000000001</v>
+        <v>6.874700000000002</v>
       </c>
       <c r="M14" t="n">
         <v>-3.8778</v>
@@ -1543,16 +1543,16 @@
         <v>-18.5563</v>
       </c>
       <c r="R14" t="n">
-        <v>5.799099999999999</v>
+        <v>5.7991</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3574</v>
+        <v>0.5098000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.1646</v>
+        <v>-2.2976</v>
       </c>
       <c r="U14" t="n">
-        <v>2.807199999999999</v>
+        <v>2.8072</v>
       </c>
       <c r="V14" t="n">
         <v>6.0078</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2445</v>
+        <v>5.436</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5414</v>
+        <v>4.7773</v>
       </c>
       <c r="F15" t="n">
-        <v>0.703</v>
+        <v>0.6586</v>
       </c>
       <c r="G15" t="n">
         <v>3.4356</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0228</v>
+        <v>0.2144</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8487</v>
+        <v>-0.6128</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8716</v>
+        <v>0.8272</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.035</v>
+        <v>3.0631</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3141</v>
+        <v>-0.1141</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7209</v>
+        <v>3.1772</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8589</v>
+        <v>0.5745</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1031</v>
+        <v>0.521</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2442</v>
+        <v>0.0535</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4335</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3599</v>
+        <v>0.911</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>-0.8366</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4254</v>
+        <v>0.5001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7432</v>
+        <v>-0.39</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3178</v>
+        <v>0.8901</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1271</v>
+        <v>0.1691</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5454</v>
+        <v>-0.1885</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5816</v>
+        <v>0.3576</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5051</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1638</v>
+        <v>2.8609</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2473</v>
+        <v>0.6148</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9166</v>
+        <v>2.2461</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1261</v>
+        <v>2.2297</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7036</v>
+        <v>-1.2366</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4225</v>
+        <v>3.4663</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8903</v>
+        <v>1.6367</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6218</v>
+        <v>-1.4649</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2685</v>
+        <v>3.1015</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2358</v>
+        <v>0.5931</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0818</v>
+        <v>0.2283</v>
       </c>
       <c r="O17" t="n">
-        <v>0.154</v>
+        <v>0.3648</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4863</v>
+        <v>-0.3842</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4832</v>
+        <v>-1.0218</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9695</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0637</v>
+        <v>1.8614</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8218</v>
+        <v>1.2473</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8855</v>
+        <v>0.6141</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5745</v>
+        <v>3.1261</v>
       </c>
       <c r="H18" t="n">
-        <v>0.521</v>
+        <v>0.7036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0535</v>
+        <v>2.4225</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07439999999999999</v>
+        <v>2.8903</v>
       </c>
       <c r="K18" t="n">
-        <v>0.911</v>
+        <v>0.6218</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8366</v>
+        <v>2.2685</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5001</v>
+        <v>0.2358</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.39</v>
+        <v>0.0818</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8901</v>
+        <v>0.154</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8303</v>
+        <v>0.1838</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8962</v>
+        <v>-0.4832</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0659</v>
+        <v>0.6671</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.041</v>
+        <v>1.8555</v>
       </c>
       <c r="E19" t="n">
-        <v>0.143</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8979</v>
+        <v>2.7209</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2297</v>
+        <v>0.8589</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2366</v>
+        <v>1.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4663</v>
+        <v>-0.2442</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6367</v>
+        <v>0.4335</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4649</v>
+        <v>0.3599</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1015</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5931</v>
+        <v>0.4254</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2283</v>
+        <v>0.7432</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3648</v>
+        <v>-0.3178</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2041</v>
+        <v>0.9476</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4936</v>
+        <v>0.3659</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2895</v>
+        <v>0.5816</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-0.6468</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.5051</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6735</v>
+        <v>0.9094</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3137</v>
+        <v>0.5496</v>
       </c>
       <c r="F20" t="n">
         <v>0.3598</v>
@@ -2014,10 +2014,10 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3813</v>
+        <v>-0.1454</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U20" t="n">
         <v>-0.1573</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5017</v>
+        <v>0.288</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0042</v>
+        <v>0.5324</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.2444</v>
       </c>
       <c r="G21" t="n">
         <v>1.1581</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.72</v>
+        <v>0.5063</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6018</v>
+        <v>0.13</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1182</v>
+        <v>0.3763</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1729</v>
+        <v>0.2287</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1231</v>
+        <v>2.8872</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9502</v>
+        <v>-2.6585</v>
       </c>
       <c r="G22" t="n">
         <v>-0.049</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.601</v>
+        <v>0.6567</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2284</v>
+        <v>-0.0075</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3725</v>
+        <v>0.6642</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0026</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2794</v>
+        <v>-0.3917</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7433</v>
+        <v>-2.9792</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4639</v>
+        <v>2.5876</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9503</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2095</v>
+        <v>0.0973</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2513</v>
+        <v>-0.4872</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4608</v>
+        <v>0.5845</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9304</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8227</v>
+        <v>-0.9635</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2944</v>
+        <v>-0.8842</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5283</v>
+        <v>-0.0794</v>
       </c>
       <c r="G24" t="n">
         <v>-2.743</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6677</v>
+        <v>0.5269</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7512</v>
+        <v>0.1614</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0835</v>
+        <v>0.3655</v>
       </c>
       <c r="V24" t="n">
         <v>0.7886</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4059</v>
+        <v>-2.3159</v>
       </c>
       <c r="E25" t="n">
         <v>-2.9246</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5187</v>
+        <v>0.6087</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9826</v>
@@ -2404,13 +2404,13 @@
         <v>1.8556</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2609</v>
+        <v>-0.1709</v>
       </c>
       <c r="T25" t="n">
         <v>-0.55</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2891</v>
+        <v>0.3791</v>
       </c>
       <c r="V25" t="n">
         <v>0.1418</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.9953</v>
+        <v>-3.8665</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.958</v>
+        <v>-3.8964</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0373</v>
+        <v>0.0299</v>
       </c>
       <c r="G26" t="n">
         <v>-5.731</v>
@@ -2482,13 +2482,13 @@
         <v>1.6237</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8004</v>
+        <v>0.3284</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.187</v>
+        <v>-0.1254</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3866</v>
+        <v>0.4538</v>
       </c>
       <c r="V26" t="n">
         <v>1.0722</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>7.392800000000001</v>
+        <v>8.965400000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-1.055299999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>8.448</v>
+        <v>10.0206</v>
       </c>
       <c r="G27" t="n">
         <v>-0.7141000000000002</v>
       </c>
       <c r="H27" t="n">
-        <v>2.682500000000001</v>
+        <v>2.682499999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-3.3967</v>
@@ -2560,13 +2560,13 @@
         <v>18.5562</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3574</v>
+        <v>2.93</v>
       </c>
       <c r="T27" t="n">
         <v>-2.8072</v>
       </c>
       <c r="U27" t="n">
-        <v>4.164499999999999</v>
+        <v>5.737200000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-6.007800000000001</v>
@@ -2575,7 +2575,7 @@
         <v>3.673</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.680900000000001</v>
+        <v>-9.680899999999999</v>
       </c>
     </row>
   </sheetData>
